--- a/tabtools/demo/demo_simtab.xlsx
+++ b/tabtools/demo/demo_simtab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="263" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="263" uniqueCount="76">
   <si>
     <t>Simulation results by scenario (400 replications)</t>
   </si>
@@ -34,7 +34,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>Coverage is empirical 95% CI coverage; * flags off-nominal coverage.</t>
+    <t>Coverage is empirical 95% CI coverage. * coverage differs from the nominal 95% by more than 2 Monte Carlo SEs</t>
   </si>
   <si>
     <t>Estimator</t>
@@ -178,9 +178,6 @@
     <t>Simulation results by scenario and estimand</t>
   </si>
   <si>
-    <t>Coverage is empirical 95% CI coverage.</t>
-  </si>
-  <si>
     <t>Marginal slope</t>
   </si>
   <si>
@@ -251,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1464">
+  <fonts count="1483">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2927,6 +2924,51 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -6220,6 +6262,56 @@
       <sz val="8"/>
       <name val="Arial"/>
       <i/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <i/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="8"/>
@@ -6480,7 +6572,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1121">
+  <borders count="1142">
     <border>
       <left/>
       <right/>
@@ -9673,6 +9765,69 @@
       <left style="none"/>
       <right style="thin"/>
       <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -9876,6 +10031,7 @@
     <border/>
     <border/>
     <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -14202,11 +14358,82 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1121">
+  <cellXfs count="1142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -16142,2489 +16369,2567 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="492" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="493" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="494" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="495" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="496" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="497" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="498" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="499" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="500" xfId="0"/>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="501" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="502" xfId="0"/>
-    <xf numFmtId="0" fontId="650" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="652" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="654" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="656" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="658" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="660" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="662" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="664" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="666" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="668" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="670" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="672" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="674" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="676" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="678" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="680" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="682" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="684" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="686" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="688" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="690" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="692" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="694" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="696" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="698" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="700" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="702" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="704" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="706" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="708" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="710" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="712" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="714" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="716" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="718" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="720" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="722" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="724" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="726" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="728" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="730" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="732" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="734" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="736" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="738" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="740" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="742" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="744" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="746" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="748" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="750" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="752" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="754" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="756" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="758" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="760" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="762" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="764" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="768" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="770" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="772" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="784" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="786" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="788" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="794" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="796" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="800" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="814" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="816" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="818" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="820" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="822" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="824" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="826" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="828" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="830" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="832" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="834" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="836" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="838" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="840" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="842" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="844" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="846" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="848" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="850" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="852" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="854" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="856" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="858" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="860" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="862" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="864" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="866" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="868" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="870" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="872" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="874" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="876" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="878" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="880" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="882" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="884" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="886" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="888" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="890" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="892" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="894" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="896" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="898" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="900" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="902" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="904" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="906" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="908" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="910" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="912" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="914" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="916" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="918" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="920" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="922" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="924" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="926" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="928" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="930" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="932" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="934" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="935" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="936" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="937" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="938" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="939" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="940" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="941" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="942" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="943" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="944" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="945" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="946" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="947" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="948" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="949" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="950" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="951" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="952" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="954" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="956" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="958" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="960" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="961" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="962" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="963" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="964" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="965" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="966" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="967" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="968" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="969" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="971" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="972" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="974" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="975" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="976" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="977" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="978" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="979" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="980" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="981" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="982" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="983" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="984" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="985" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="986" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="987" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="988" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="989" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="990" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="991" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="992" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="993" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="994" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="995" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="996" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="997" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="998" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="999" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1000" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1001" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1002" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1003" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1004" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1005" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1006" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1007" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1008" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1009" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1010" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1011" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1012" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1013" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1014" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1015" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1016" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1017" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1018" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1019" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1020" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1021" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1022" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1023" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1024" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1025" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1026" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1027" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1028" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1029" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1030" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1031" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1032" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1033" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1034" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1035" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1036" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1037" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1038" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1039" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1040" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1041" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1042" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1043" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1044" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1045" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1046" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1047" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1048" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1049" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1050" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1051" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1052" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1053" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1054" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1055" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1056" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1057" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1058" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1059" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1060" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1061" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1062" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1063" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1064" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1065" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1066" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1067" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1068" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1069" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1070" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1071" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1072" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1073" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1074" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1075" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1076" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1077" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1078" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="503" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="504" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="505" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="506" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="507" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="508" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="509" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="510" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="511" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="512" xfId="0"/>
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="817" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="965" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1079" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1080" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1081" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1082" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1083" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1084" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1085" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1086" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1095" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1087" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1088" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1097" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1089" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1090" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1099" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1091" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1092" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1101" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1093" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1094" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1103" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1095" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1096" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1097" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1098" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1099" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1100" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1101" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1102" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1103" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1104" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1105" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1106" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1107" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1108" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1109" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1110" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1111" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1112" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1113" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1114" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1115" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1116" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1117" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1118" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1119" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1120" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1121" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1122" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1123" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1124" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1125" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1126" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1127" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1128" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1129" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1130" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1131" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1132" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1133" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1134" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1135" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1136" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1137" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1138" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1139" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1140" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1141" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1142" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1143" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1144" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1145" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1146" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1147" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1148" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1149" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1150" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1151" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1152" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1153" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1154" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1155" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1156" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1157" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1158" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1159" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1160" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1161" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1162" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1163" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1164" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1165" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1166" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1167" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1169" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1171" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1173" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1175" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1177" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1179" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1181" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1183" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1185" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1187" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1189" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1191" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1193" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1195" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1197" fillId="0" borderId="893" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1199" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1201" fillId="0" borderId="895" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1203" fillId="0" borderId="896" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1205" fillId="0" borderId="897" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1207" fillId="0" borderId="898" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1209" fillId="0" borderId="899" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1211" fillId="0" borderId="900" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1212" fillId="0" borderId="901" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1105" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1107" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1109" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1111" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1113" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1115" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1117" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1119" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1121" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1123" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1125" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1127" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1129" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1131" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1133" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1135" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1137" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1139" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1141" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1143" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1145" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1147" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1149" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1151" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1152" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1153" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1154" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1155" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1156" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1157" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1158" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1159" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1160" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1161" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1162" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1163" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1164" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1165" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1166" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1167" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1168" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1169" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1170" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1171" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1172" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1173" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1174" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1175" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1176" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1178" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1180" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1182" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1184" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1186" fillId="0" borderId="893" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1188" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1190" fillId="0" borderId="895" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1192" fillId="0" borderId="896" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1194" fillId="0" borderId="897" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1196" fillId="0" borderId="898" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1198" fillId="0" borderId="899" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1200" fillId="0" borderId="900" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1202" fillId="0" borderId="901" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1204" fillId="0" borderId="902" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1206" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1208" fillId="0" borderId="904" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1210" fillId="0" borderId="905" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1212" fillId="0" borderId="906" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1214" fillId="0" borderId="907" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1216" fillId="0" borderId="908" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1218" fillId="0" borderId="909" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1220" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1221" fillId="0" borderId="911" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1213" fillId="0" borderId="902" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1222" fillId="0" borderId="912" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1214" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1223" fillId="0" borderId="913" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1215" fillId="0" borderId="904" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1224" fillId="0" borderId="914" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1216" fillId="0" borderId="905" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1225" fillId="0" borderId="915" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1217" fillId="0" borderId="906" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1226" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1218" fillId="0" borderId="907" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1227" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1219" fillId="0" borderId="908" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1228" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1220" fillId="0" borderId="909" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1229" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1221" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1230" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1222" fillId="0" borderId="911" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1231" fillId="0" borderId="921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1224" fillId="0" borderId="912" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1225" fillId="0" borderId="913" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1233" fillId="0" borderId="922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1234" fillId="0" borderId="923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1227" fillId="0" borderId="914" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1228" fillId="0" borderId="915" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1236" fillId="0" borderId="924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1237" fillId="0" borderId="925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1229" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1230" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1231" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1238" fillId="0" borderId="926" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1239" fillId="0" borderId="927" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1240" fillId="0" borderId="928" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1232" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1233" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1234" fillId="0" borderId="921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1235" fillId="0" borderId="922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1241" fillId="0" borderId="929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1242" fillId="0" borderId="930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1243" fillId="0" borderId="931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1244" fillId="0" borderId="932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1236" fillId="0" borderId="923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1237" fillId="0" borderId="924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1238" fillId="0" borderId="925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1240" fillId="0" borderId="926" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1242" fillId="0" borderId="927" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1244" fillId="0" borderId="928" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1246" fillId="0" borderId="929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1248" fillId="0" borderId="930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1250" fillId="0" borderId="931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1252" fillId="0" borderId="932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1254" fillId="0" borderId="933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1256" fillId="0" borderId="934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1258" fillId="0" borderId="935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1259" fillId="0" borderId="936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1245" fillId="0" borderId="933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1246" fillId="0" borderId="934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1247" fillId="0" borderId="935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1249" fillId="0" borderId="936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1251" fillId="0" borderId="937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1253" fillId="0" borderId="938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1255" fillId="0" borderId="939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1257" fillId="0" borderId="940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1259" fillId="0" borderId="941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1261" fillId="0" borderId="942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1263" fillId="0" borderId="943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1265" fillId="0" borderId="944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1267" fillId="0" borderId="945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1268" fillId="0" borderId="946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1260" fillId="0" borderId="937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1269" fillId="0" borderId="947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1261" fillId="0" borderId="938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1270" fillId="0" borderId="948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1262" fillId="0" borderId="939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1271" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1263" fillId="0" borderId="940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1272" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1264" fillId="0" borderId="941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1273" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1265" fillId="0" borderId="942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1274" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1266" fillId="0" borderId="943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1275" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1267" fillId="0" borderId="944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1276" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1268" fillId="0" borderId="945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1277" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1269" fillId="0" borderId="946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1270" fillId="0" borderId="947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1271" fillId="0" borderId="948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1278" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1279" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1280" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1272" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1273" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1274" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1275" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1281" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1282" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1283" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1284" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1276" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1277" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1278" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1279" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1285" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1286" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1287" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1288" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1280" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1289" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1281" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1290" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1282" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1291" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1283" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1292" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1284" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1293" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1285" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1294" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1286" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1295" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1287" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1296" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1288" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1297" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1289" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1298" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1290" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1299" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1291" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1292" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1293" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1294" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1295" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1296" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1297" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1298" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1299" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1300" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1300" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1301" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1302" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1303" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1304" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1305" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1306" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1307" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1308" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1309" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1301" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1310" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1302" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1311" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1303" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1312" fillId="0" borderId="990" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1304" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1313" fillId="0" borderId="991" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1305" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1314" fillId="0" borderId="992" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1306" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1315" fillId="0" borderId="993" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1307" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1316" fillId="0" borderId="994" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1308" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1317" fillId="0" borderId="995" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1309" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1318" fillId="0" borderId="996" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1310" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1311" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1319" fillId="0" borderId="997" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1320" fillId="0" borderId="998" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1312" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1321" fillId="0" borderId="999" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1313" fillId="0" borderId="990" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1322" fillId="0" borderId="1000" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1314" fillId="0" borderId="991" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1323" fillId="0" borderId="1001" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1315" fillId="0" borderId="992" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1324" fillId="0" borderId="1002" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1316" fillId="0" borderId="993" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1325" fillId="0" borderId="1003" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1317" fillId="0" borderId="994" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1326" fillId="0" borderId="1004" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1318" fillId="0" borderId="995" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1327" fillId="0" borderId="1005" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1319" fillId="0" borderId="996" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1328" fillId="0" borderId="1006" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1320" fillId="0" borderId="997" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1329" fillId="0" borderId="1007" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1321" fillId="0" borderId="998" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1322" fillId="0" borderId="999" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1330" fillId="0" borderId="1008" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1331" fillId="0" borderId="1009" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1323" fillId="0" borderId="1000" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1324" fillId="0" borderId="1001" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1325" fillId="0" borderId="1002" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1326" fillId="0" borderId="1003" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1327" fillId="0" borderId="1004" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1328" fillId="0" borderId="1005" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1329" fillId="0" borderId="1006" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1330" fillId="0" borderId="1007" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1331" fillId="0" borderId="1008" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1332" fillId="0" borderId="1009" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1333" fillId="0" borderId="1010" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1332" fillId="0" borderId="1010" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1333" fillId="0" borderId="1011" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1334" fillId="0" borderId="1012" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1335" fillId="0" borderId="1013" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1336" fillId="0" borderId="1014" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1337" fillId="0" borderId="1015" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1338" fillId="0" borderId="1016" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1339" fillId="0" borderId="1017" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1340" fillId="0" borderId="1018" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1341" fillId="0" borderId="1019" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1342" fillId="0" borderId="1020" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1334" fillId="0" borderId="1011" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1343" fillId="0" borderId="1021" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1335" fillId="0" borderId="1012" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1344" fillId="0" borderId="1022" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1336" fillId="0" borderId="1013" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1345" fillId="0" borderId="1023" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1337" fillId="0" borderId="1014" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1346" fillId="0" borderId="1024" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1338" fillId="0" borderId="1015" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1347" fillId="0" borderId="1025" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1339" fillId="0" borderId="1016" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1348" fillId="0" borderId="1026" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1340" fillId="0" borderId="1017" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1349" fillId="0" borderId="1027" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1341" fillId="0" borderId="1018" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1350" fillId="0" borderId="1028" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1342" fillId="0" borderId="1019" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1351" fillId="0" borderId="1029" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1343" fillId="0" borderId="1020" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1344" fillId="0" borderId="1021" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1352" fillId="0" borderId="1030" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1353" fillId="0" borderId="1031" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1345" fillId="0" borderId="1022" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1346" fillId="0" borderId="1023" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1347" fillId="0" borderId="1024" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1348" fillId="0" borderId="1025" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1349" fillId="0" borderId="1026" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1350" fillId="0" borderId="1027" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1351" fillId="0" borderId="1028" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1352" fillId="0" borderId="1029" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1353" fillId="0" borderId="1030" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1354" fillId="0" borderId="1031" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1354" fillId="0" borderId="1032" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1355" fillId="0" borderId="1033" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1356" fillId="0" borderId="1034" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1357" fillId="0" borderId="1035" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1358" fillId="0" borderId="1036" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1359" fillId="0" borderId="1037" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1360" fillId="0" borderId="1038" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1361" fillId="0" borderId="1039" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1362" fillId="0" borderId="1040" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1363" fillId="0" borderId="1041" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1355" fillId="0" borderId="1032" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1364" fillId="0" borderId="1042" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1356" fillId="0" borderId="1033" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1357" fillId="0" borderId="1034" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1358" fillId="0" borderId="1035" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1359" fillId="0" borderId="1036" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1360" fillId="0" borderId="1037" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1361" fillId="0" borderId="1038" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1362" fillId="0" borderId="1039" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1363" fillId="0" borderId="1040" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1364" fillId="0" borderId="1041" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1365" fillId="0" borderId="1043" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1366" fillId="0" borderId="1044" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1367" fillId="0" borderId="1045" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1368" fillId="0" borderId="1046" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1369" fillId="0" borderId="1047" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1370" fillId="0" borderId="1048" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1371" fillId="0" borderId="1049" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1372" fillId="0" borderId="1050" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1373" fillId="0" borderId="1051" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1365" fillId="0" borderId="1042" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1374" fillId="0" borderId="1052" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1366" fillId="0" borderId="1043" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1367" fillId="0" borderId="1044" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1368" fillId="0" borderId="1045" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1369" fillId="0" borderId="1046" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1370" fillId="0" borderId="1047" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1371" fillId="0" borderId="1048" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1372" fillId="0" borderId="1049" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1373" fillId="0" borderId="1050" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1374" fillId="2" borderId="1051" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1375" fillId="0" borderId="1053" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1376" fillId="0" borderId="1054" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1377" fillId="0" borderId="1055" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1378" fillId="0" borderId="1056" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1379" fillId="0" borderId="1057" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1380" fillId="0" borderId="1058" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1381" fillId="0" borderId="1059" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1382" fillId="0" borderId="1060" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1383" fillId="2" borderId="1061" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1375" fillId="3" borderId="1052" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1384" fillId="3" borderId="1062" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1376" fillId="4" borderId="1053" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1377" fillId="5" borderId="1054" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1378" fillId="6" borderId="1055" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1379" fillId="7" borderId="1056" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1380" fillId="8" borderId="1057" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1381" fillId="9" borderId="1058" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1382" fillId="10" borderId="1059" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1383" fillId="11" borderId="1060" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1384" fillId="12" borderId="1061" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1385" fillId="4" borderId="1063" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1386" fillId="5" borderId="1064" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1387" fillId="6" borderId="1065" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1388" fillId="7" borderId="1066" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1389" fillId="8" borderId="1067" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1390" fillId="9" borderId="1068" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1391" fillId="10" borderId="1069" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1392" fillId="11" borderId="1070" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1393" fillId="12" borderId="1071" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1385" fillId="13" borderId="1062" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1394" fillId="13" borderId="1072" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1386" fillId="14" borderId="1063" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1387" fillId="15" borderId="1064" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1388" fillId="16" borderId="1065" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1389" fillId="17" borderId="1066" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1390" fillId="18" borderId="1067" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1391" fillId="19" borderId="1068" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1392" fillId="20" borderId="1069" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1393" fillId="21" borderId="1070" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1394" fillId="22" borderId="1071" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1395" fillId="14" borderId="1073" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1396" fillId="15" borderId="1074" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1397" fillId="16" borderId="1075" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1398" fillId="17" borderId="1076" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1399" fillId="18" borderId="1077" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1400" fillId="19" borderId="1078" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1401" fillId="20" borderId="1079" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1402" fillId="21" borderId="1080" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1403" fillId="22" borderId="1081" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1395" fillId="23" borderId="1072" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1404" fillId="23" borderId="1082" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1396" fillId="24" borderId="1073" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1397" fillId="25" borderId="1074" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1398" fillId="26" borderId="1075" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1399" fillId="27" borderId="1076" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1400" fillId="28" borderId="1077" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1401" fillId="29" borderId="1078" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1402" fillId="30" borderId="1079" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1403" fillId="31" borderId="1080" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1404" fillId="32" borderId="1081" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1405" fillId="24" borderId="1083" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1406" fillId="25" borderId="1084" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1407" fillId="26" borderId="1085" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1408" fillId="27" borderId="1086" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1409" fillId="28" borderId="1087" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1410" fillId="29" borderId="1088" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1411" fillId="30" borderId="1089" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1412" fillId="31" borderId="1090" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1413" fillId="32" borderId="1091" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1405" fillId="33" borderId="1082" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1414" fillId="33" borderId="1092" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1406" fillId="34" borderId="1083" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1407" fillId="35" borderId="1084" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1408" fillId="36" borderId="1085" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1409" fillId="37" borderId="1086" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1410" fillId="38" borderId="1087" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1411" fillId="39" borderId="1088" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1412" fillId="40" borderId="1089" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1413" fillId="41" borderId="1090" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1415" fillId="0" borderId="1091" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1417" fillId="0" borderId="1092" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1419" fillId="0" borderId="1093" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1421" fillId="0" borderId="1094" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1423" fillId="0" borderId="1095" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1425" fillId="0" borderId="1096" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1427" fillId="0" borderId="1097" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1429" fillId="0" borderId="1098" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1431" fillId="0" borderId="1099" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1433" fillId="0" borderId="1100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1435" fillId="0" borderId="1101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1437" fillId="0" borderId="1102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1439" fillId="0" borderId="1103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1441" fillId="0" borderId="1104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1443" fillId="0" borderId="1105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1445" fillId="0" borderId="1106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1447" fillId="0" borderId="1107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1449" fillId="0" borderId="1108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1451" fillId="0" borderId="1109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1453" fillId="0" borderId="1110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1454" fillId="0" borderId="1111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1415" fillId="34" borderId="1093" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1416" fillId="35" borderId="1094" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1417" fillId="36" borderId="1095" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1418" fillId="37" borderId="1096" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1419" fillId="38" borderId="1097" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1420" fillId="39" borderId="1098" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1421" fillId="40" borderId="1099" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1422" fillId="41" borderId="1100" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1424" fillId="0" borderId="1101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1426" fillId="0" borderId="1102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1428" fillId="0" borderId="1103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1430" fillId="0" borderId="1104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1432" fillId="0" borderId="1105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1434" fillId="0" borderId="1106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1436" fillId="0" borderId="1107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1438" fillId="0" borderId="1108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1440" fillId="0" borderId="1109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1442" fillId="0" borderId="1110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1444" fillId="0" borderId="1111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1446" fillId="0" borderId="1112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1448" fillId="0" borderId="1113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1450" fillId="0" borderId="1114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1452" fillId="0" borderId="1115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1454" fillId="0" borderId="1116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1456" fillId="0" borderId="1117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1458" fillId="0" borderId="1118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1460" fillId="0" borderId="1119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1462" fillId="0" borderId="1120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1463" fillId="0" borderId="1121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1455" fillId="0" borderId="1112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1464" fillId="0" borderId="1122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1456" fillId="0" borderId="1113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1465" fillId="0" borderId="1123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1457" fillId="0" borderId="1114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1466" fillId="0" borderId="1124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1458" fillId="0" borderId="1115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1467" fillId="0" borderId="1125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1459" fillId="0" borderId="1116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1468" fillId="0" borderId="1126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1460" fillId="0" borderId="1117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1469" fillId="0" borderId="1127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1461" fillId="0" borderId="1118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1470" fillId="0" borderId="1128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1462" fillId="0" borderId="1119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1471" fillId="0" borderId="1129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1463" fillId="0" borderId="1120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1472" fillId="0" borderId="1130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1473" fillId="0" borderId="1131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1474" fillId="0" borderId="1132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1475" fillId="0" borderId="1133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1476" fillId="0" borderId="1134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1477" fillId="0" borderId="1135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1478" fillId="0" borderId="1136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1479" fillId="0" borderId="1137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1480" fillId="0" borderId="1138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1481" fillId="0" borderId="1139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1482" fillId="0" borderId="1140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1141" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19001,35 +19306,35 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="501" customFormat="true" ht="30" customHeight="true">
       <c r="A12" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="483" t="s">
+      <c r="B12" s="492" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="484" t="s">
+      <c r="C12" s="493" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="485" t="s">
+      <c r="D12" s="494" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="486" t="s">
+      <c r="E12" s="495" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="487" t="s">
+      <c r="F12" s="496" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="488" t="s">
+      <c r="G12" s="497" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="489" t="s">
+      <c r="H12" s="498" t="s">
         <v>1</v>
       </c>
-      <c r="I12" s="490" t="s">
+      <c r="I12" s="499" t="s">
         <v>1</v>
       </c>
-      <c r="J12" s="491" t="s">
+      <c r="J12" s="500" t="s">
         <v>1</v>
       </c>
     </row>
@@ -19046,471 +19351,471 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="492" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="493" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="494" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="495" customWidth="true"/>
-    <col min="5" max="5" width="8.7109375" style="496" customWidth="true"/>
-    <col min="6" max="6" width="10.7109375" style="497" customWidth="true"/>
-    <col min="7" max="7" width="8.7109375" style="498" customWidth="true"/>
-    <col min="8" max="8" width="8.7109375" style="499" customWidth="true"/>
-    <col min="9" max="9" width="8.7109375" style="500" customWidth="true"/>
-    <col min="10" max="10" width="10.7109375" style="501" customWidth="true"/>
-    <col min="11" max="11" width="8.7109375" style="502" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="502" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="503" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="504" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="505" customWidth="true"/>
+    <col min="5" max="5" width="8.7109375" style="506" customWidth="true"/>
+    <col min="6" max="6" width="10.7109375" style="507" customWidth="true"/>
+    <col min="7" max="7" width="8.7109375" style="508" customWidth="true"/>
+    <col min="8" max="8" width="8.7109375" style="509" customWidth="true"/>
+    <col min="9" max="9" width="8.7109375" style="510" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" style="511" customWidth="true"/>
+    <col min="11" max="11" width="8.7109375" style="512" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="901" t="s">
+      <c r="A1" s="911" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="902" t="s">
+      <c r="B1" s="912" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="903" t="s">
+      <c r="C1" s="913" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="904" t="s">
+      <c r="D1" s="914" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="905" t="s">
+      <c r="E1" s="915" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="906" t="s">
+      <c r="F1" s="916" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="907" t="s">
+      <c r="G1" s="917" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="908" t="s">
+      <c r="H1" s="918" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="909" t="s">
+      <c r="I1" s="919" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="910" t="s">
+      <c r="J1" s="920" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="911" t="s">
+      <c r="K1" s="921" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="657" t="s">
+      <c r="A2" s="667" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1009" t="s">
+      <c r="B2" s="1019" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="987" t="s">
+      <c r="C2" s="997" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="948" t="s">
+      <c r="D2" s="958" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="959" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="960" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1008" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="962" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="949" t="s">
+      <c r="I2" s="963" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="950" t="s">
+      <c r="J2" s="964" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="998" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="952" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="953" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="954" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1020" t="s">
+      <c r="K2" s="1030" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="668" t="s">
+      <c r="A3" s="678" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1010" t="s">
+      <c r="B3" s="1020" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="988" t="s">
+      <c r="C3" s="998" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="958" t="s">
+      <c r="D3" s="968" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="959" t="s">
+      <c r="E3" s="969" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="960" t="s">
+      <c r="F3" s="970" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="999" t="s">
+      <c r="G3" s="1009" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="962" t="s">
+      <c r="H3" s="972" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="963" t="s">
+      <c r="I3" s="973" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="964" t="s">
+      <c r="J3" s="974" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="1021" t="s">
+      <c r="K3" s="1031" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="679" t="s">
+      <c r="A4" s="689" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1011" t="s">
+      <c r="B4" s="1021" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="989" t="s">
+      <c r="C4" s="999" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="807" t="s">
+      <c r="D4" s="817" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="808" t="s">
+      <c r="E4" s="818" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="809" t="s">
+      <c r="F4" s="819" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="1000" t="s">
+      <c r="G4" s="1010" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="811" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="812" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="813" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" s="1022" t="s">
+      <c r="H4" s="821" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="822" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="823" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="1032" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="690" t="s">
+      <c r="A5" s="700" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1051" t="s">
+      <c r="B5" s="1061" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1052" t="s">
+      <c r="C5" s="1062" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1053" t="s">
+      <c r="D5" s="1063" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1054" t="s">
+      <c r="E5" s="1064" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1055" t="s">
+      <c r="F5" s="1065" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="1056" t="s">
+      <c r="G5" s="1066" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="1057" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="1058" t="s">
+      <c r="H5" s="1067" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="1068" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="1059" t="s">
+      <c r="J5" s="1069" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="1060" t="s">
+      <c r="K5" s="1070" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="701" t="s">
+      <c r="A6" s="711" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1013" t="s">
+      <c r="B6" s="1023" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="991" t="s">
+      <c r="C6" s="1001" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="823" t="s">
+      <c r="D6" s="833" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="824" t="s">
+      <c r="E6" s="834" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="825" t="s">
+      <c r="F6" s="835" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="1002" t="s">
+      <c r="G6" s="1012" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="827" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="828" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="829" t="s">
+      <c r="H6" s="837" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="838" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="839" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="1024" t="s">
+      <c r="K6" s="1034" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="712" t="s">
+      <c r="A7" s="722" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1061" t="s">
+      <c r="B7" s="1071" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1062" t="s">
+      <c r="C7" s="1072" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1063" t="s">
+      <c r="D7" s="1073" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="1064" t="s">
+      <c r="E7" s="1074" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="1065" t="s">
+      <c r="F7" s="1075" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="1066" t="s">
+      <c r="G7" s="1076" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="1067" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="1068" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="1069" t="s">
-        <v>72</v>
-      </c>
-      <c r="K7" s="1070" t="s">
-        <v>76</v>
+      <c r="H7" s="1077" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="1078" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="1079" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="1080" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="723" t="s">
+      <c r="A8" s="733" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="1015" t="s">
+      <c r="B8" s="1025" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="993" t="s">
+      <c r="C8" s="1003" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="839" t="s">
+      <c r="D8" s="849" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="840" t="s">
+      <c r="E8" s="850" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="841" t="s">
+      <c r="F8" s="851" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="1004" t="s">
+      <c r="G8" s="1014" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="843" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="844" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="845" t="s">
-        <v>73</v>
-      </c>
-      <c r="K8" s="1026" t="s">
+      <c r="H8" s="853" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="854" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="855" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="1036" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="734" t="s">
+      <c r="A9" s="744" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1071" t="s">
+      <c r="B9" s="1081" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="1072" t="s">
+      <c r="C9" s="1082" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1073" t="s">
+      <c r="D9" s="1083" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1074" t="s">
+      <c r="E9" s="1084" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1075" t="s">
+      <c r="F9" s="1085" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="1076" t="s">
+      <c r="G9" s="1086" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="1077" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="1078" t="s">
+      <c r="H9" s="1087" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="1088" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="1079" t="s">
+      <c r="J9" s="1089" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="1080" t="s">
+      <c r="K9" s="1090" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="745" t="s">
+      <c r="A10" s="755" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="1041" t="s">
+      <c r="B10" s="1051" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="1042" t="s">
+      <c r="C10" s="1052" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="1043" t="s">
+      <c r="D10" s="1053" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1044" t="s">
+      <c r="E10" s="1054" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="1045" t="s">
+      <c r="F10" s="1055" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="1046" t="s">
+      <c r="G10" s="1056" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="1047" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="1048" t="s">
+      <c r="H10" s="1057" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="1058" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="1049" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="1050" t="s">
-        <v>76</v>
+      <c r="J10" s="1059" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="1060" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="756" t="s">
+      <c r="A11" s="766" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="1081" t="s">
+      <c r="B11" s="1091" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="1082" t="s">
+      <c r="C11" s="1092" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1083" t="s">
+      <c r="D11" s="1093" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="1084" t="s">
+      <c r="E11" s="1094" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="1085" t="s">
+      <c r="F11" s="1095" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="1086" t="s">
+      <c r="G11" s="1096" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="1087" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="1088" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="1089" t="s">
+      <c r="H11" s="1097" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="1098" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="1099" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="1090" t="s">
+      <c r="K11" s="1100" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="767" t="s">
+      <c r="A12" s="777" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="1019" t="s">
+      <c r="B12" s="1029" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="997" t="s">
+      <c r="C12" s="1007" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="968" t="s">
+      <c r="D12" s="978" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="969" t="s">
+      <c r="E12" s="979" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="970" t="s">
+      <c r="F12" s="980" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="1008" t="s">
+      <c r="G12" s="1018" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="972" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="973" t="s">
+      <c r="H12" s="982" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="983" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="974" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="1030" t="s">
+      <c r="J12" s="984" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="1040" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="778" t="s">
+    <row r="13" s="1141" customFormat="true" ht="30" customHeight="true">
+      <c r="A13" s="788" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="1111" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="1112" t="s">
+      <c r="B13" s="1131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1132" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="1113" t="s">
+      <c r="D13" s="1133" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="1114" t="s">
+      <c r="E13" s="1134" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="1115" t="s">
+      <c r="F13" s="1135" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="1116" t="s">
+      <c r="G13" s="1136" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="1117" t="s">
+      <c r="H13" s="1137" t="s">
         <v>1</v>
       </c>
-      <c r="I13" s="1118" t="s">
+      <c r="I13" s="1138" t="s">
         <v>1</v>
       </c>
-      <c r="J13" s="1119" t="s">
+      <c r="J13" s="1139" t="s">
         <v>1</v>
       </c>
-      <c r="K13" s="1120" t="s">
+      <c r="K13" s="1140" t="s">
         <v>1</v>
       </c>
     </row>
